--- a/西陇/order/知识库/2.0版本（11月）/XL-客户业务关系（V1.1）_备份.xlsx
+++ b/西陇/order/知识库/2.0版本（11月）/XL-客户业务关系（V1.1）_备份.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12500"/>
+    <workbookView windowWidth="29080" windowHeight="8520"/>
   </bookViews>
   <sheets>
     <sheet name="客户信息表schema (2)" sheetId="1" r:id="rId1"/>
@@ -1394,7 +1394,7 @@
     <col min="10" max="21" width="13.671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.2" spans="1:9">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
